--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45331</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>43654</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>43843</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>43936</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>44319</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44727</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43734,7 +43734,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48743,7 +48743,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49142,7 +49142,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50099,7 +50099,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50156,7 +50156,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51217,7 +51217,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51755,7 +51755,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52221,7 +52221,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52620,7 +52620,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52853,7 +52853,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53081,7 +53081,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54526,7 +54526,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55101,7 +55101,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55163,7 +55163,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56727,7 +56727,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56898,7 +56898,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56955,7 +56955,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57069,7 +57069,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57302,7 +57302,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57706,7 +57706,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57763,7 +57763,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58581,7 +58581,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58752,7 +58752,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58921,14 +58921,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58978,14 +58978,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58998,7 +58998,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59035,14 +59035,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59055,7 +59055,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59092,14 +59092,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59112,7 +59112,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59149,14 +59149,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59169,7 +59169,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59206,14 +59206,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59263,14 +59263,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59327,7 +59327,7 @@
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59384,7 +59384,7 @@
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59441,7 +59441,7 @@
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59555,7 +59555,7 @@
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59605,14 +59605,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 5581-2024</t>
+          <t>A 5578-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59625,7 +59625,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59662,14 +59662,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 5578-2024</t>
+          <t>A 5581-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -59726,7 +59726,7 @@
         <v>45335</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2421,14 +2421,14 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5354-2024</t>
+          <t>A 24677-2022</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45331</v>
+        <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -2450,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2468,12 +2468,104 @@
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Vedskivlav
+Dropptaggsvamp
+Orre</t>
+        </is>
+      </c>
+      <c r="S21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 24677-2022 artfynd.xlsx", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="T21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 24677-2022 karta.png", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="V21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 24677-2022 FSC-klagomål.docx", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 24677-2022 FSC-klagomål mail.docx", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 24677-2022 tillsynsbegäran.docx", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 24677-2022 tillsynsbegäran mail.docx", "A 24677-2022")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 24677-2022 prioriterade fågelarter.docx", "A 24677-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 5354-2024</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Rynkskinn
 Kilporing
@@ -2481,480 +2573,393 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="S21">
+      <c r="S22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 5354-2024 artfynd.xlsx", "A 5354-2024")</f>
         <v/>
       </c>
-      <c r="T21">
+      <c r="T22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 5354-2024 karta.png", "A 5354-2024")</f>
         <v/>
       </c>
-      <c r="V21">
+      <c r="V22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 5354-2024 FSC-klagomål.docx", "A 5354-2024")</f>
         <v/>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 5354-2024 FSC-klagomål mail.docx", "A 5354-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 5354-2024 tillsynsbegäran.docx", "A 5354-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 5354-2024 tillsynsbegäran mail.docx", "A 5354-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 35545-2019</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B23" s="1" t="n">
         <v>43654</v>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="C23" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>2.7</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tallticka
 Gullgröppa</t>
         </is>
       </c>
-      <c r="S22">
+      <c r="S23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 35545-2019 artfynd.xlsx", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="T22">
+      <c r="T23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 35545-2019 karta.png", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="V22">
+      <c r="V23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 35545-2019 FSC-klagomål.docx", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 35545-2019 FSC-klagomål mail.docx", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 35545-2019 tillsynsbegäran.docx", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 35545-2019 tillsynsbegäran mail.docx", "A 35545-2019")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/fåglar/A 35545-2019 prioriterade fågelarter.docx", "A 35545-2019")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 1309-2020</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B24" s="1" t="n">
         <v>43843</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="C24" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>16.5</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3</v>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Vedskivlav
 Nästlav
 Revlummer</t>
         </is>
       </c>
-      <c r="S23">
+      <c r="S24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 1309-2020 artfynd.xlsx", "A 1309-2020")</f>
         <v/>
       </c>
-      <c r="T23">
+      <c r="T24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 1309-2020 karta.png", "A 1309-2020")</f>
         <v/>
       </c>
-      <c r="V23">
+      <c r="V24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 1309-2020 FSC-klagomål.docx", "A 1309-2020")</f>
         <v/>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 1309-2020 FSC-klagomål mail.docx", "A 1309-2020")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 1309-2020 tillsynsbegäran.docx", "A 1309-2020")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 1309-2020 tillsynsbegäran mail.docx", "A 1309-2020")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 19244-2020</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B25" s="1" t="n">
         <v>43936</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="C25" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>13.7</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Brandticka
 Småskölding</t>
         </is>
       </c>
-      <c r="S24">
+      <c r="S25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 19244-2020 artfynd.xlsx", "A 19244-2020")</f>
         <v/>
       </c>
-      <c r="T24">
+      <c r="T25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 19244-2020 karta.png", "A 19244-2020")</f>
         <v/>
       </c>
-      <c r="V24">
+      <c r="V25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 19244-2020 FSC-klagomål.docx", "A 19244-2020")</f>
         <v/>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 19244-2020 FSC-klagomål mail.docx", "A 19244-2020")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 19244-2020 tillsynsbegäran.docx", "A 19244-2020")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 19244-2020 tillsynsbegäran mail.docx", "A 19244-2020")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 20838-2021</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B26" s="1" t="n">
         <v>44319</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="C26" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>1.9</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Rödgul trumpetsvamp
 Toppvaxskivling</t>
         </is>
       </c>
-      <c r="S25">
+      <c r="S26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 20838-2021 artfynd.xlsx", "A 20838-2021")</f>
         <v/>
       </c>
-      <c r="T25">
+      <c r="T26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 20838-2021 karta.png", "A 20838-2021")</f>
         <v/>
       </c>
-      <c r="V25">
+      <c r="V26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 20838-2021 FSC-klagomål.docx", "A 20838-2021")</f>
         <v/>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 20838-2021 FSC-klagomål mail.docx", "A 20838-2021")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 20838-2021 tillsynsbegäran.docx", "A 20838-2021")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 20838-2021 tillsynsbegäran mail.docx", "A 20838-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 24677-2022</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Vedskivlav
-Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="S26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/artfynd/A 24677-2022 artfynd.xlsx", "A 24677-2022")</f>
-        <v/>
-      </c>
-      <c r="T26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/kartor/A 24677-2022 karta.png", "A 24677-2022")</f>
-        <v/>
-      </c>
-      <c r="V26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomål/A 24677-2022 FSC-klagomål.docx", "A 24677-2022")</f>
-        <v/>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/klagomålsmail/A 24677-2022 FSC-klagomål mail.docx", "A 24677-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsyn/A 24677-2022 tillsynsbegäran.docx", "A 24677-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1880/tillsynsmail/A 24677-2022 tillsynsbegäran mail.docx", "A 24677-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -2965,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3057,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3144,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3231,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3322,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3412,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3498,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3584,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3675,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3761,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3847,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3933,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4115,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4200,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4375,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4465,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4555,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4640,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4725,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4810,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4900,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4985,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5160,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5249,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5339,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5424,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5514,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5599,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5684,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5769,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5854,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5939,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6118,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6208,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6293,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6378,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6463,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6553,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6638,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6723,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6808,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6893,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6978,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7067,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7161,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7246,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7336,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7421,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7483,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7540,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7597,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7654,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7716,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7778,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7835,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7892,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7949,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8006,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8063,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8120,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8177,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8234,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8291,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8348,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8405,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8462,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8519,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8576,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8633,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8690,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8747,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8804,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8861,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8918,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8975,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9032,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9089,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9146,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9203,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9260,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9317,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9374,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9431,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9488,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9545,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9602,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9659,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9716,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9773,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9830,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9887,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9944,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10001,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10058,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10115,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10172,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10234,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10296,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10353,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10410,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10472,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10529,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10591,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10648,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10705,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10762,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10819,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10876,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10933,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10990,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11047,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11109,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11171,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11233,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11295,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11352,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11409,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11466,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11523,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11580,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11637,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11694,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11751,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11808,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11865,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11922,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11979,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12036,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12093,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12150,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12207,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12264,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12321,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12378,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12435,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12492,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12549,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12606,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12663,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12720,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12777,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12834,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12891,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12948,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13005,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13062,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13119,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13176,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13233,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13290,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13347,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13404,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13461,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13518,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13575,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13632,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13689,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13746,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13803,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13860,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13917,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13974,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14031,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14088,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14145,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14202,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14259,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14316,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14393,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14450,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14512,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14574,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14631,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14693,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14750,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14812,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14869,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14926,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14988,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15045,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15102,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15159,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15216,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15273,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15330,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15387,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15444,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15501,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15558,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15615,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15672,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15729,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15786,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15843,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15900,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15957,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16014,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16071,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16128,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16185,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16242,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16304,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16361,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16418,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16480,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16537,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16599,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16661,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16718,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16775,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16832,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16889,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16946,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17008,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17065,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17127,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17184,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17241,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17298,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17355,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17412,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17474,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17531,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17588,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17645,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17702,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17759,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17816,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17873,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17930,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17987,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18049,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18106,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18168,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18225,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18282,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18339,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18396,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18453,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18510,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18567,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18629,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18691,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18748,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18805,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18862,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18919,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18976,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19033,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19090,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19147,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19204,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19261,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19318,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19375,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19432,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19489,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19546,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19603,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19660,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19717,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19774,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19831,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19888,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19945,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20002,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20059,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20116,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20178,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20235,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20292,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20349,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20406,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20463,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20520,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20577,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20634,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20691,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20748,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20805,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20862,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20924,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20981,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21043,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21105,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21162,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21219,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21276,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21338,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21395,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21452,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21509,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21566,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21628,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21685,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21742,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21799,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21856,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21913,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21975,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22032,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22089,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22146,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22203,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22260,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22317,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22374,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22431,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22488,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22545,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22602,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22664,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22726,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22783,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22840,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23011,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23068,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23125,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23182,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23239,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23296,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23353,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23410,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23467,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23524,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23581,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23638,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23695,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23752,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23809,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23866,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23928,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23990,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24052,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24114,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24171,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24228,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24285,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24342,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24399,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24461,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24523,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24580,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24637,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24694,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24751,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24808,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24865,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24922,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24979,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25036,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25098,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25155,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25217,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25274,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25331,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25388,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25445,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25502,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25559,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25616,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25678,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25735,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25792,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25849,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25906,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25963,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26020,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26077,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26134,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26191,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26248,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26310,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26367,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26424,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26481,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26543,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26600,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26657,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26714,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26776,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26838,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26900,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26957,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27014,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27071,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27128,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27185,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27242,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27299,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27356,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27413,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27470,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27527,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27584,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27641,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27698,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27755,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27812,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27869,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27926,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27983,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28040,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28097,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28154,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28211,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28268,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28325,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28382,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28439,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28496,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28553,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28615,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28672,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28734,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28791,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28848,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28905,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28962,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29019,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29076,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29133,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29190,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29247,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29304,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29366,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29423,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29480,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29542,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29599,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29656,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29718,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29775,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29832,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29889,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29946,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30003,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30060,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30122,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30179,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30241,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30303,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30365,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30427,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30489,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30551,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30613,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30670,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30727,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30789,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30846,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30903,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30960,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31017,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31074,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31136,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31193,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31250,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31307,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31369,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31426,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31483,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31540,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31597,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31654,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31711,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31768,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31825,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31887,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31944,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32001,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32058,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32115,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32172,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32229,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32286,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32343,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32405,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32462,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32519,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32581,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32638,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32695,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32752,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32809,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32866,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32923,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32980,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33037,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33094,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33151,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33208,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33265,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33322,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33379,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33436,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33493,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33550,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33607,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33664,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33721,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33778,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33835,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33892,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33949,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34006,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34063,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34120,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34177,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34234,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34291,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34348,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34405,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34462,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34519,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34576,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34633,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34690,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34747,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34804,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34861,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34918,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34975,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35032,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35089,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35146,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35203,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35260,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35317,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35374,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35431,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35488,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35545,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35602,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35664,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35721,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35778,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35835,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35892,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35949,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36006,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36063,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36120,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36177,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36234,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36291,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36353,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36410,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36467,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36529,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36586,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36643,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36700,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36762,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36819,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36876,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36933,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36990,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37047,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37104,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37161,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37218,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37275,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37332,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37389,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37446,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37503,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37560,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37617,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37674,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37731,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37793,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37850,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37907,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37964,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38026,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38083,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38140,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38197,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38254,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38311,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38368,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38425,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38482,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38539,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38596,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38653,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38710,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38767,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38829,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38886,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38948,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39005,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39062,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39119,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39176,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39233,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39295,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39352,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39414,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39471,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39528,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39590,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39652,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39714,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39776,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39838,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39900,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39957,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40014,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40071,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40133,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40190,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40247,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40304,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40361,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40418,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40475,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40532,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40589,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40646,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40703,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40760,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40817,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40874,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40931,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40988,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41045,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41102,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41159,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41216,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41273,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41330,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41387,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41444,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41501,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41558,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41615,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41672,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41729,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41786,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41843,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41900,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41957,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42019,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42076,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42133,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42190,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42247,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42304,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42361,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42418,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42475,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42537,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42594,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42651,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42708,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42765,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42822,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42879,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42936,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42993,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43050,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43107,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43164,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43221,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43278,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43335,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43392,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43449,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43506,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43563,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43620,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43677,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43734,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43791,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43848,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43905,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43962,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44019,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44076,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44133,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44190,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44247,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44309,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44366,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44423,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44480,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44537,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44594,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44651,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44708,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44765,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44822,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44879,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44936,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44993,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45050,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45107,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45164,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45221,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45283,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45345,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45402,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45459,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45516,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45573,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45630,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45687,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45744,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45801,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45858,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45915,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45972,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46029,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46086,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46143,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46200,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46257,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46314,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46371,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46428,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46485,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46542,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46599,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46661,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46718,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46775,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46832,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46889,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46946,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47003,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47060,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47117,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47174,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47231,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47288,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47345,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47402,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47459,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47516,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47573,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47630,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47687,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47744,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47801,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47858,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47920,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47982,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48044,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48101,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48158,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48215,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48272,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48329,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48386,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48443,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48500,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48557,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48619,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48681,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48743,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48800,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48857,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48914,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48971,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49028,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49085,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49142,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49199,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49256,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49318,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49380,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49442,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49499,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49556,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49613,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49675,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49737,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49799,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49861,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49923,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49985,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50042,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50099,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50156,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50213,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50275,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50337,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50394,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50451,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50508,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50565,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50622,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50679,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50741,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50803,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50865,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50927,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50984,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51041,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51098,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51160,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51217,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51274,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51331,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51388,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51450,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51512,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51574,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51636,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51698,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51755,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51812,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51869,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51931,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51993,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52050,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52107,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52164,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52221,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52278,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52335,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52392,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52449,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52506,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52563,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52620,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52677,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52734,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52796,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52853,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52910,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52967,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53024,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53081,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53138,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53195,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53252,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53309,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53366,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53423,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53485,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53542,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53599,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53656,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53713,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53770,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53827,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53884,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53941,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53998,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54055,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54112,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54174,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54231,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54293,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54355,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54412,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54469,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54526,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54583,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54645,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54702,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54759,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54816,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54873,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54930,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54987,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55044,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55101,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55163,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55225,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55287,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55344,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55406,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55463,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55520,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55577,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55634,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55691,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55753,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55810,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55867,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55924,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55981,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56038,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56095,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56152,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56209,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56266,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56328,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56385,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56442,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56499,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56556,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56613,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56670,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56727,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56784,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56841,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56898,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56955,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57012,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57069,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57126,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57183,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57240,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57302,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57364,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57421,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57478,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57535,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57592,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57649,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57706,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57763,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57825,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57887,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57944,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58001,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58058,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58120,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58182,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58239,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58296,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58353,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58410,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58467,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58524,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58581,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58638,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58695,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58752,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58809,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58871,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58921,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58941,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58978,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58998,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59035,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59055,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59092,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59112,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59149,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59169,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59206,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59226,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59263,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59283,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59327,7 +59332,7 @@
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59384,7 +59389,7 @@
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59441,7 +59446,7 @@
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59498,7 +59503,7 @@
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59555,7 +59560,7 @@
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59612,7 +59617,7 @@
         <v>45334</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59669,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59726,7 +59731,7 @@
         <v>45335</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z983"/>
+  <dimension ref="A1:Z986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5357-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59610,14 +59610,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 5578-2024</t>
+          <t>A 5357-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59674,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59721,62 +59721,243 @@
       </c>
       <c r="R982" s="2" t="inlineStr"/>
     </row>
-    <row r="983">
+    <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
+          <t>A 5578-2024</t>
+        </is>
+      </c>
+      <c r="B983" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="C983" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G983" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H983" t="n">
+        <v>0</v>
+      </c>
+      <c r="I983" t="n">
+        <v>0</v>
+      </c>
+      <c r="J983" t="n">
+        <v>0</v>
+      </c>
+      <c r="K983" t="n">
+        <v>0</v>
+      </c>
+      <c r="L983" t="n">
+        <v>0</v>
+      </c>
+      <c r="M983" t="n">
+        <v>0</v>
+      </c>
+      <c r="N983" t="n">
+        <v>0</v>
+      </c>
+      <c r="O983" t="n">
+        <v>0</v>
+      </c>
+      <c r="P983" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q983" t="n">
+        <v>0</v>
+      </c>
+      <c r="R983" s="2" t="inlineStr"/>
+    </row>
+    <row r="984" ht="15" customHeight="1">
+      <c r="A984" t="inlineStr">
+        <is>
           <t>A 5795-2024</t>
         </is>
       </c>
-      <c r="B983" s="1" t="n">
+      <c r="B984" s="1" t="n">
         <v>45335</v>
       </c>
-      <c r="C983" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D983" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="E983" t="inlineStr">
-        <is>
-          <t>ÖREBRO</t>
-        </is>
-      </c>
-      <c r="G983" t="n">
+      <c r="C984" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G984" t="n">
         <v>1.8</v>
       </c>
-      <c r="H983" t="n">
-        <v>0</v>
-      </c>
-      <c r="I983" t="n">
-        <v>0</v>
-      </c>
-      <c r="J983" t="n">
-        <v>0</v>
-      </c>
-      <c r="K983" t="n">
-        <v>0</v>
-      </c>
-      <c r="L983" t="n">
-        <v>0</v>
-      </c>
-      <c r="M983" t="n">
-        <v>0</v>
-      </c>
-      <c r="N983" t="n">
-        <v>0</v>
-      </c>
-      <c r="O983" t="n">
-        <v>0</v>
-      </c>
-      <c r="P983" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q983" t="n">
-        <v>0</v>
-      </c>
-      <c r="R983" s="2" t="inlineStr"/>
+      <c r="H984" t="n">
+        <v>0</v>
+      </c>
+      <c r="I984" t="n">
+        <v>0</v>
+      </c>
+      <c r="J984" t="n">
+        <v>0</v>
+      </c>
+      <c r="K984" t="n">
+        <v>0</v>
+      </c>
+      <c r="L984" t="n">
+        <v>0</v>
+      </c>
+      <c r="M984" t="n">
+        <v>0</v>
+      </c>
+      <c r="N984" t="n">
+        <v>0</v>
+      </c>
+      <c r="O984" t="n">
+        <v>0</v>
+      </c>
+      <c r="P984" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q984" t="n">
+        <v>0</v>
+      </c>
+      <c r="R984" s="2" t="inlineStr"/>
+    </row>
+    <row r="985" ht="15" customHeight="1">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>A 6586-2024</t>
+        </is>
+      </c>
+      <c r="B985" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C985" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G985" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H985" t="n">
+        <v>0</v>
+      </c>
+      <c r="I985" t="n">
+        <v>0</v>
+      </c>
+      <c r="J985" t="n">
+        <v>0</v>
+      </c>
+      <c r="K985" t="n">
+        <v>0</v>
+      </c>
+      <c r="L985" t="n">
+        <v>0</v>
+      </c>
+      <c r="M985" t="n">
+        <v>0</v>
+      </c>
+      <c r="N985" t="n">
+        <v>0</v>
+      </c>
+      <c r="O985" t="n">
+        <v>0</v>
+      </c>
+      <c r="P985" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q985" t="n">
+        <v>0</v>
+      </c>
+      <c r="R985" s="2" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>A 6592-2024</t>
+        </is>
+      </c>
+      <c r="B986" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C986" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G986" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H986" t="n">
+        <v>0</v>
+      </c>
+      <c r="I986" t="n">
+        <v>0</v>
+      </c>
+      <c r="J986" t="n">
+        <v>0</v>
+      </c>
+      <c r="K986" t="n">
+        <v>0</v>
+      </c>
+      <c r="L986" t="n">
+        <v>0</v>
+      </c>
+      <c r="M986" t="n">
+        <v>0</v>
+      </c>
+      <c r="N986" t="n">
+        <v>0</v>
+      </c>
+      <c r="O986" t="n">
+        <v>0</v>
+      </c>
+      <c r="P986" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q986" t="n">
+        <v>0</v>
+      </c>
+      <c r="R986" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z986"/>
+  <dimension ref="A1:Z987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59617,7 +59617,7 @@
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
       </c>
       <c r="R985" s="2" t="inlineStr"/>
     </row>
-    <row r="986">
+    <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
           <t>A 6592-2024</t>
@@ -59907,7 +59907,7 @@
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59958,6 +59958,63 @@
         <v>0</v>
       </c>
       <c r="R986" s="2" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>A 6879-2024</t>
+        </is>
+      </c>
+      <c r="B987" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C987" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G987" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H987" t="n">
+        <v>0</v>
+      </c>
+      <c r="I987" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" t="n">
+        <v>0</v>
+      </c>
+      <c r="K987" t="n">
+        <v>0</v>
+      </c>
+      <c r="L987" t="n">
+        <v>0</v>
+      </c>
+      <c r="M987" t="n">
+        <v>0</v>
+      </c>
+      <c r="N987" t="n">
+        <v>0</v>
+      </c>
+      <c r="O987" t="n">
+        <v>0</v>
+      </c>
+      <c r="P987" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q987" t="n">
+        <v>0</v>
+      </c>
+      <c r="R987" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59275,7 +59275,7 @@
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59617,7 +59617,7 @@
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59838,14 +59838,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6586-2024</t>
+          <t>A 6592-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -59900,14 +59900,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6592-2024</t>
+          <t>A 6586-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5357-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59610,14 +59610,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 5357-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59667,14 +59667,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 5581-2024</t>
+          <t>A 5578-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -59724,14 +59724,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 5578-2024</t>
+          <t>A 5581-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59838,14 +59838,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6592-2024</t>
+          <t>A 6586-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -59900,14 +59900,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6586-2024</t>
+          <t>A 6592-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59104,7 +59104,7 @@
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5357-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59610,14 +59610,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5357-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59674,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59907,7 +59907,7 @@
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59332,7 +59332,7 @@
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59446,7 +59446,7 @@
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59560,7 +59560,7 @@
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59838,14 +59838,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6586-2024</t>
+          <t>A 6592-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -59900,14 +59900,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6592-2024</t>
+          <t>A 6586-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z987"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5342-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5352-2024</t>
+          <t>A 5357-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59553,14 +59553,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5342-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -59610,14 +59610,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 5357-2024</t>
+          <t>A 5352-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -59667,14 +59667,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 5578-2024</t>
+          <t>A 5581-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -59724,14 +59724,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 5581-2024</t>
+          <t>A 5578-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59838,14 +59838,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6592-2024</t>
+          <t>A 6586-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -59900,14 +59900,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6586-2024</t>
+          <t>A 6592-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59925,7 +59925,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -59959,7 +59959,7 @@
       </c>
       <c r="R986" s="2" t="inlineStr"/>
     </row>
-    <row r="987">
+    <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
           <t>A 6879-2024</t>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60015,6 +60015,234 @@
         <v>0</v>
       </c>
       <c r="R987" s="2" t="inlineStr"/>
+    </row>
+    <row r="988" ht="15" customHeight="1">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>A 7608-2024</t>
+        </is>
+      </c>
+      <c r="B988" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C988" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G988" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H988" t="n">
+        <v>0</v>
+      </c>
+      <c r="I988" t="n">
+        <v>0</v>
+      </c>
+      <c r="J988" t="n">
+        <v>0</v>
+      </c>
+      <c r="K988" t="n">
+        <v>0</v>
+      </c>
+      <c r="L988" t="n">
+        <v>0</v>
+      </c>
+      <c r="M988" t="n">
+        <v>0</v>
+      </c>
+      <c r="N988" t="n">
+        <v>0</v>
+      </c>
+      <c r="O988" t="n">
+        <v>0</v>
+      </c>
+      <c r="P988" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q988" t="n">
+        <v>0</v>
+      </c>
+      <c r="R988" s="2" t="inlineStr"/>
+    </row>
+    <row r="989" ht="15" customHeight="1">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>A 7611-2024</t>
+        </is>
+      </c>
+      <c r="B989" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C989" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G989" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H989" t="n">
+        <v>0</v>
+      </c>
+      <c r="I989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" t="n">
+        <v>0</v>
+      </c>
+      <c r="K989" t="n">
+        <v>0</v>
+      </c>
+      <c r="L989" t="n">
+        <v>0</v>
+      </c>
+      <c r="M989" t="n">
+        <v>0</v>
+      </c>
+      <c r="N989" t="n">
+        <v>0</v>
+      </c>
+      <c r="O989" t="n">
+        <v>0</v>
+      </c>
+      <c r="P989" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q989" t="n">
+        <v>0</v>
+      </c>
+      <c r="R989" s="2" t="inlineStr"/>
+    </row>
+    <row r="990" ht="15" customHeight="1">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>A 7609-2024</t>
+        </is>
+      </c>
+      <c r="B990" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C990" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G990" t="n">
+        <v>1</v>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" t="n">
+        <v>0</v>
+      </c>
+      <c r="K990" t="n">
+        <v>0</v>
+      </c>
+      <c r="L990" t="n">
+        <v>0</v>
+      </c>
+      <c r="M990" t="n">
+        <v>0</v>
+      </c>
+      <c r="N990" t="n">
+        <v>0</v>
+      </c>
+      <c r="O990" t="n">
+        <v>0</v>
+      </c>
+      <c r="P990" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q990" t="n">
+        <v>0</v>
+      </c>
+      <c r="R990" s="2" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>A 7634-2024</t>
+        </is>
+      </c>
+      <c r="B991" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C991" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>ÖREBRO</t>
+        </is>
+      </c>
+      <c r="G991" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K991" t="n">
+        <v>0</v>
+      </c>
+      <c r="L991" t="n">
+        <v>0</v>
+      </c>
+      <c r="M991" t="n">
+        <v>0</v>
+      </c>
+      <c r="N991" t="n">
+        <v>0</v>
+      </c>
+      <c r="O991" t="n">
+        <v>0</v>
+      </c>
+      <c r="P991" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q991" t="n">
+        <v>0</v>
+      </c>
+      <c r="R991" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>43368</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>43375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>43376</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>43381</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>43389</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>43391</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>43398</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>43398</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>43399</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>43402</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>43409</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>43412</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>43418</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>43420</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>43420</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>43420</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>43430</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>43430</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>43430</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>43430</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>43433</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>43436</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>43437</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>43438</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>43438</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>43440</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43441</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43444</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43446</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43446</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>43446</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>43446</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>43447</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>43447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>43447</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>43447</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>43447</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>43447</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>43451</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>43451</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>43452</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>43454</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>43454</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>43455</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>43473</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>43476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>43480</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>43481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>43481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>43482</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>43482</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>43486</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>43486</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>43486</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>43486</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43489</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43494</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43494</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43495</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43495</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43495</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43495</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>43501</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>43508</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>43514</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>43514</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>43516</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>43518</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>43518</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>43518</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43518</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43518</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43521</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43522</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43528</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43530</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43531</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>43538</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>43541</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>43543</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>43544</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>43551</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43552</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43552</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>43552</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>43552</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>43552</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>43552</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>43552</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>43552</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>43557</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>43563</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>43563</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>43563</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>43563</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>43563</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>43563</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>43563</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>43571</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>43572</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>43581</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43584</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>43584</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43585</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>43594</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>43598</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>43605</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43612</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43619</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43627</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>43641</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>43642</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>43644</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>43647</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>43648</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>43650</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>43654</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>43655</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43655</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>43658</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>43658</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>43665</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>43665</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>43669</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>43669</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>43669</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>43676</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>43677</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>43677</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>43677</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>43683</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>43683</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>43685</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>43686</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>43689</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>43689</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>43690</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>43691</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>43691</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>43691</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>43691</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43698</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43704</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>43704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>43704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>43705</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>43710</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>43710</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>43710</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43710</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>43710</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>43710</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>43713</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>43714</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43714</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43714</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43719</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43719</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43729</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43733</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43734</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43734</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43734</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43735</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43735</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43739</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43745</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43748</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43755</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>43761</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>43766</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>43768</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>43774</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>43775</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>43776</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>43782</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>43783</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>43783</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43784</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43786</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43787</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43790</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>43790</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>43794</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>43796</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>43797</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>43801</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>43801</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>43801</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>43801</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>43803</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>43804</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43809</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43809</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43810</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43814</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>43814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>43814</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>43814</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>43818</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>43818</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>43836</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>43838</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>43840</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>43843</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>43844</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>43844</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>43844</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>43844</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>43844</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>43844</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>43844</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>43844</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>43851</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>43853</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>43853</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>43853</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>43854</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>43857</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>43858</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>43859</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>43864</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>43864</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>43866</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>43867</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>43867</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>43868</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>43868</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>43872</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>43877</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>43878</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>43878</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>43881</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>43881</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>43881</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>43881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>43894</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>43894</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>43895</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>43897</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>43897</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>43901</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>43902</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>43905</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>43907</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>43916</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>43917</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>43920</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>43927</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>43928</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>43938</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>43938</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>43951</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>43961</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>43971</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>43983</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>43983</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>43987</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>43990</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>43994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>43994</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>43997</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>43997</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>43997</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>43997</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>43998</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>43998</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44004</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44012</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>44012</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44012</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44014</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>44020</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44020</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>44020</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>44020</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44043</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>44053</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44053</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44056</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44061</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44061</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44062</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44063</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44064</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44064</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44067</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44069</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44069</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44071</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44076</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>44078</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44078</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44084</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44085</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44088</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44088</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44088</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44091</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44095</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>44095</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>44095</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44101</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44104</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44104</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44119</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44124</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44125</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44131</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44133</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>44139</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44145</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44147</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44151</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44152</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44155</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44161</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44162</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44162</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44162</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>44166</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>44173</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44179</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>44182</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44188</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44195</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>44216</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44216</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44216</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44216</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44218</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44230</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44232</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>44232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44235</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44238</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27874,7 +27874,7 @@
         <v>44244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>44244</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>44244</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44244</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44244</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44245</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44245</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>44245</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44245</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44245</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>44251</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44257</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>44271</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>44272</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>44274</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>44277</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44278</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44285</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44285</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>44292</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44295</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>44311</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>44313</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44313</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44323</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>44334</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>44340</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44342</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>44342</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>44343</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44343</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44345</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44345</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44345</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44347</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44348</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44350</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44357</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44357</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>44358</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44368</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44378</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44378</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44378</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44386</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44398</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44404</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44419</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>44420</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>44420</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44420</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44424</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44427</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44428</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44434</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>44435</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>44445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44446</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>44449</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44453</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44462</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>44464</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>44475</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>44483</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44487</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44491</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44498</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>44504</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>44505</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44509</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44511</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>44517</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>44519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>44522</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44522</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44532</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44534</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44536</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44537</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44537</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>44537</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>44538</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44539</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44539</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44539</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44539</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44539</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44539</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33441,7 +33441,7 @@
         <v>44539</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44539</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>44539</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>44545</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44545</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>44552</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44572</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44573</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44580</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44582</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>44585</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44592</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44593</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>44593</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>44593</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44595</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44595</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44596</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44601</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>44602</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44606</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44609</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>44609</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44609</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44609</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44614</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44616</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44616</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44616</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44616</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>44621</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>44631</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>44635</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44638</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>44643</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>44643</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>44647</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44648</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>44649</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>44649</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>44655</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>44656</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>44656</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44659</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44659</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44662</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44664</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44664</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36534,7 +36534,7 @@
         <v>44670</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44670</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>44671</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>44673</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44673</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44673</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44676</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44676</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44676</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44683</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44684</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44685</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44686</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44687</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44691</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44693</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44695</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44696</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44701</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>44704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44706</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>44712</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>44714</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>44721</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>44722</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44722</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44722</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>44727</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>44732</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44733</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44734</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>44746</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44748</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>44750</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44750</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>44750</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44750</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>44750</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44753</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44755</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>44761</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44764</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44764</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44781</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44781</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44781</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>44792</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>44795</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44796</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44802</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44807</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>44807</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44807</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44807</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44807</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44807</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44811</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44814</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44814</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44820</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44830</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44831</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44831</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44834</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44834</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44834</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44837</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44839</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44839</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44839</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44839</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44839</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>44839</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>44839</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44847</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44847</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>44851</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>44852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44855</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44855</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44861</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44861</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44861</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44862</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44868</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44868</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44873</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44879</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44886</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44888</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>44895</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>44895</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44897</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44901</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>44902</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44902</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44902</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44902</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44910</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44914</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>44915</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44922</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>44936</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44938</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44939</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>44941</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>44941</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42998,7 +42998,7 @@
         <v>44942</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44942</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44944</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>44944</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44951</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44951</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44951</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>44951</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44952</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>44952</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>44953</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>44956</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>44958</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>44963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44966</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44138,7 +44138,7 @@
         <v>44966</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44966</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>44977</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44980</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44983</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>44984</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>44987</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>44990</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>44990</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44990</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>44990</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44992</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44993</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44993</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44993</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>44998</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44998</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44998</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45000</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45000</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45004</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45004</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45006</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45010</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45010</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45010</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45012</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45012</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45012</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45013</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45013</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45013</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45013</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45013</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45016</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45021</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45021</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45021</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45027</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45027</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45028</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45029</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45030</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45030</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>45030</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45030</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>45033</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45036</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>45036</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45040</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45042</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45042</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45042</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45042</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45043</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45043</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45050</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>45054</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45055</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45055</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45056</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45063</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45069</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45069</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45070</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45070</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45071</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45075</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45077</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45077</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45077</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45077</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45078</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45079</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45093</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>45096</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45098</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45103</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45104</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45109</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45111</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45112</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>45112</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45112</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45114</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45114</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45114</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45114</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45114</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45114</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45118</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45118</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45118</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45119</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45119</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45119</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>45119</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45119</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45119</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45119</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45119</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45120</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45125</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45127</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>45127</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45127</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45131</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>45131</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>45131</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45131</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45131</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45132</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45132</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45132</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51393,7 +51393,7 @@
         <v>45134</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45134</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45135</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45135</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>45135</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45138</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45141</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45145</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45147</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45147</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45152</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45161</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45162</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45162</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45162</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45162</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45162</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45163</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45165</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45167</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45167</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45170</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45174</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45175</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45175</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45175</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45177</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45177</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45180</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45180</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45181</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45184</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45187</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45189</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45189</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45191</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45194</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45196</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45197</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45197</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45197</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45197</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45202</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45205</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45210</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45210</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45213</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45216</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45216</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45219</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45219</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45219</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45219</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45219</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45223</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45224</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54821,7 +54821,7 @@
         <v>45229</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45229</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45229</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45229</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45229</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>45230</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45230</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45230</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45233</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45233</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>45233</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55468,7 +55468,7 @@
         <v>45235</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45236</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>45236</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45238</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45239</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45239</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45245</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45246</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45246</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>45246</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45247</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45247</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45251</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45251</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45251</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45251</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45251</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>45252</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45252</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45254</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>45257</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>45257</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45257</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45257</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>45257</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45258</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>45258</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45258</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45258</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45265</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45268</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45268</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45272</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45273</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>45274</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45281</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45281</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45283</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45287</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45290</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45290</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45292</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45294</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45294</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45299</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45299</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45300</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45300</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45300</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>45301</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45301</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45302</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45302</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>45302</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58643,7 +58643,7 @@
         <v>45306</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45307</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45321</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58814,7 +58814,7 @@
         <v>45322</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45328</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58926,14 +58926,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 5127-2024</t>
+          <t>A 5136-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -58983,14 +58983,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 5136-2024</t>
+          <t>A 5113-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -59040,14 +59040,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 5135-2024</t>
+          <t>A 5125-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -59097,14 +59097,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 5113-2024</t>
+          <t>A 5129-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -59154,14 +59154,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 5125-2024</t>
+          <t>A 5133-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -59211,14 +59211,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 5129-2024</t>
+          <t>A 5127-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -59268,14 +59268,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 5133-2024</t>
+          <t>A 5135-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -59325,14 +59325,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 5330-2024</t>
+          <t>A 5324-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -59382,14 +59382,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 5338-2024</t>
+          <t>A 5330-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -59439,14 +59439,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 5357-2024</t>
+          <t>A 5338-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -59496,14 +59496,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 5324-2024</t>
+          <t>A 5357-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -59560,7 +59560,7 @@
         <v>45331</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45331</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59667,14 +59667,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 5581-2024</t>
+          <t>A 5578-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -59724,14 +59724,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 5578-2024</t>
+          <t>A 5581-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -59788,7 +59788,7 @@
         <v>45335</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>45341</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59907,7 +59907,7 @@
         <v>45341</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>45348</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -60076,14 +60076,14 @@
     <row r="989" ht="15" customHeight="1">
       <c r="A989" t="inlineStr">
         <is>
-          <t>A 7611-2024</t>
+          <t>A 7634-2024</t>
         </is>
       </c>
       <c r="B989" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         </is>
       </c>
       <c r="G989" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="H989" t="n">
         <v>0</v>
@@ -60140,7 +60140,7 @@
         <v>45348</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -60190,14 +60190,14 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>A 7634-2024</t>
+          <t>A 7611-2024</t>
         </is>
       </c>
       <c r="B991" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         </is>
       </c>
       <c r="G991" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="H991" t="n">
         <v>0</v>

--- a/Översikt ÖREBRO.xlsx
+++ b/Översikt ÖREBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z991"/>
+  <dimension ref="A1:Z993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44707</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>43558</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>44522</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>44365</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>44379</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>43691</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>43539</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>43719</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>44340</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>43605</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>43691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>43795</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>43360</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44700</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>43643</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>44245</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>44727</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45331</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>43654</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>43843</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43936</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44319</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>44753</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44783</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44951</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>45012</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>43495</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>43518</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>43572</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43719</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44214</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44244</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44616</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44753</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45215</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>43356</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>43452</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>43541</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>43644</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43696</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>43826</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>43843</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>43844</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>43858</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>43905</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>43980</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>43986</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>43997</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43998</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44004</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44146</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44218</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44237</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44244</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44245</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44285</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44375</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44435</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44482</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44593</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44643</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44740</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44755</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44839</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44958</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>45054</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45055</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45072</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>45077</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45114</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45119</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45330</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>43321</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43325</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>43327</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>43327</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>43329</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>43336</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43336</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>43353</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>43357</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>43361</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>43363</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>